--- a/12612645.xlsx
+++ b/12612645.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shash\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shash\Desktop\Activities\12612645\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D25AC879-399D-4B9B-A23C-E5B4A4DDFF76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB4100D1-70C7-45B6-AC12-2C3F04509A49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -233,6 +233,12 @@
   </si>
   <si>
     <t>Sickness came back, so all I did was studying at my room.</t>
+  </si>
+  <si>
+    <t>Good</t>
+  </si>
+  <si>
+    <t>It was a good day, learnt few new things.</t>
   </si>
 </sst>
 </file>
@@ -1246,27 +1252,51 @@
         <v>65</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+    <row r="11" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="8">
+        <v>46256</v>
+      </c>
+      <c r="B11" s="14">
+        <v>240</v>
+      </c>
+      <c r="C11" s="14">
+        <v>0</v>
+      </c>
+      <c r="D11" s="14">
+        <v>390</v>
+      </c>
+      <c r="E11" s="14">
+        <v>180</v>
+      </c>
+      <c r="F11" s="14">
+        <v>0</v>
+      </c>
+      <c r="G11" s="14">
+        <v>0</v>
+      </c>
+      <c r="H11" s="14">
+        <v>240</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
+        <v>390</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="13"/>

--- a/12612645.xlsx
+++ b/12612645.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shash\Desktop\Activities\12612645\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB4100D1-70C7-45B6-AC12-2C3F04509A49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AA6C1EF-81E9-4DC8-95F1-460358620639}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1299,47 +1299,91 @@
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="A12" s="8">
+        <v>46257</v>
+      </c>
+      <c r="B12" s="14">
+        <v>300</v>
+      </c>
+      <c r="C12" s="14">
+        <v>0</v>
+      </c>
+      <c r="D12" s="14">
+        <v>360</v>
+      </c>
+      <c r="E12" s="14">
+        <v>260</v>
+      </c>
+      <c r="F12" s="14">
+        <v>0</v>
+      </c>
+      <c r="G12" s="14">
+        <v>0</v>
+      </c>
+      <c r="H12" s="14">
+        <v>180</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>1100</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
+        <v>340</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>61</v>
+      </c>
       <c r="N12" s="17"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="8">
+        <v>46258</v>
+      </c>
+      <c r="B13" s="14">
+        <v>270</v>
+      </c>
+      <c r="C13" s="14">
+        <v>0</v>
+      </c>
+      <c r="D13" s="14">
+        <v>210</v>
+      </c>
+      <c r="E13" s="14">
+        <v>0</v>
+      </c>
+      <c r="F13" s="14">
+        <v>200</v>
+      </c>
+      <c r="G13" s="14">
+        <v>4</v>
+      </c>
+      <c r="H13" s="14">
+        <v>60</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>740</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
+        <v>700</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N13" s="17"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">

--- a/12612645.xlsx
+++ b/12612645.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shash\Desktop\Activities\12612645\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AA6C1EF-81E9-4DC8-95F1-460358620639}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9116BEBD-DD20-4802-8971-FCBA94B1D3F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1353,7 +1353,7 @@
         <v>0</v>
       </c>
       <c r="D13" s="14">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="E13" s="14">
         <v>0</v>
@@ -1369,11 +1369,11 @@
       </c>
       <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v>740</v>
+        <v>770</v>
       </c>
       <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v>700</v>
+        <v>670</v>
       </c>
       <c r="K13" s="16" t="s">
         <v>57</v>

--- a/12612645.xlsx
+++ b/12612645.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shash\Desktop\Activities\12612645\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9116BEBD-DD20-4802-8971-FCBA94B1D3F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4329C332-CEAA-44A5-9BA1-CECE70EBEBC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -239,6 +239,12 @@
   </si>
   <si>
     <t>It was a good day, learnt few new things.</t>
+  </si>
+  <si>
+    <t>Stressed</t>
+  </si>
+  <si>
+    <t>The whole day was stressful because I couldn't sleep at night.</t>
   </si>
 </sst>
 </file>
@@ -1386,27 +1392,51 @@
       </c>
       <c r="N13" s="17"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+    <row r="14" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="8">
+        <v>46259</v>
+      </c>
+      <c r="B14" s="14">
+        <v>60</v>
+      </c>
+      <c r="C14" s="14">
+        <v>0</v>
+      </c>
+      <c r="D14" s="14">
+        <v>180</v>
+      </c>
+      <c r="E14" s="14">
+        <v>150</v>
+      </c>
+      <c r="F14" s="14">
+        <v>350</v>
+      </c>
+      <c r="G14" s="14">
+        <v>7</v>
+      </c>
+      <c r="H14" s="14">
+        <v>0</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>740</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+        <v>700</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>

--- a/12612645.xlsx
+++ b/12612645.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shash\Desktop\Activities\12612645\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4329C332-CEAA-44A5-9BA1-CECE70EBEBC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3866817-9130-42A5-9F50-6498BA51E2FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -245,6 +245,9 @@
   </si>
   <si>
     <t>The whole day was stressful because I couldn't sleep at night.</t>
+  </si>
+  <si>
+    <t>I was sick the whole day. Not productive day I would say.</t>
   </si>
 </sst>
 </file>
@@ -1438,27 +1441,51 @@
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+    <row r="15" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="8">
+        <v>46260</v>
+      </c>
+      <c r="B15" s="14">
+        <v>420</v>
+      </c>
+      <c r="C15" s="14">
+        <v>0</v>
+      </c>
+      <c r="D15" s="14">
+        <v>210</v>
+      </c>
+      <c r="E15" s="14">
+        <v>90</v>
+      </c>
+      <c r="F15" s="14">
+        <v>0</v>
+      </c>
+      <c r="G15" s="14">
+        <v>0</v>
+      </c>
+      <c r="H15" s="14">
+        <v>0</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>720</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+        <v>720</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="13"/>

--- a/12612645.xlsx
+++ b/12612645.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shash\Desktop\Activities\12612645\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3866817-9130-42A5-9F50-6498BA51E2FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{468FDA77-FC7A-426B-ABE4-89D206817225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -248,6 +248,9 @@
   </si>
   <si>
     <t>I was sick the whole day. Not productive day I would say.</t>
+  </si>
+  <si>
+    <t>Sickness continued.</t>
   </si>
 </sst>
 </file>
@@ -1488,26 +1491,50 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="A16" s="8">
+        <v>46261</v>
+      </c>
+      <c r="B16" s="14">
+        <v>540</v>
+      </c>
+      <c r="C16" s="14">
+        <v>0</v>
+      </c>
+      <c r="D16" s="14">
+        <v>300</v>
+      </c>
+      <c r="E16" s="14">
+        <v>200</v>
+      </c>
+      <c r="F16" s="14">
+        <v>0</v>
+      </c>
+      <c r="G16" s="14">
+        <v>0</v>
+      </c>
+      <c r="H16" s="14">
+        <v>0</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+        <v>400</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="13"/>

--- a/12612645.xlsx
+++ b/12612645.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shash\Desktop\Activities\12612645\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{468FDA77-FC7A-426B-ABE4-89D206817225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BE94736-FA45-4150-93D4-29E4EE948DD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -214,43 +214,43 @@
     <t xml:space="preserve">Felt so tired in last two lectures. </t>
   </si>
   <si>
-    <t>Couldn't have enough sleep today as well. But learnt few new things.</t>
-  </si>
-  <si>
     <t>Excellent</t>
   </si>
   <si>
     <t>High</t>
   </si>
   <si>
-    <t>I had a severe fever</t>
-  </si>
-  <si>
     <t>Very Satisfied</t>
-  </si>
-  <si>
-    <t>I was energetic for the whole day despite having cold and fever.</t>
-  </si>
-  <si>
-    <t>Sickness came back, so all I did was studying at my room.</t>
   </si>
   <si>
     <t>Good</t>
   </si>
   <si>
-    <t>It was a good day, learnt few new things.</t>
-  </si>
-  <si>
     <t>Stressed</t>
   </si>
   <si>
-    <t>The whole day was stressful because I couldn't sleep at night.</t>
+    <t>NA</t>
   </si>
   <si>
-    <t>I was sick the whole day. Not productive day I would say.</t>
+    <t>Couldn’t get enough sleep today either, but at least I learned a few new things.</t>
   </si>
   <si>
-    <t>Sickness continued.</t>
+    <t>I had a pretty bad fever.</t>
+  </si>
+  <si>
+    <t>Excellent day, was full of energy.</t>
+  </si>
+  <si>
+    <t>Sickness came back, so all I did was study in my room.</t>
+  </si>
+  <si>
+    <t>It was a good day. Learned a few new things about the scope of variables at the memory level.</t>
+  </si>
+  <si>
+    <t>Exhausting.</t>
+  </si>
+  <si>
+    <t>Not a productive day I would say.</t>
   </si>
 </sst>
 </file>
@@ -1041,8 +1041,8 @@
       <c r="B6" s="9">
         <v>240</v>
       </c>
-      <c r="C6" s="9">
-        <v>0</v>
+      <c r="C6" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D6" s="9">
         <v>240</v>
@@ -1087,8 +1087,8 @@
       <c r="B7" s="14">
         <v>180</v>
       </c>
-      <c r="C7" s="14">
-        <v>0</v>
+      <c r="C7" s="14" t="s">
+        <v>64</v>
       </c>
       <c r="D7" s="14">
         <v>240</v>
@@ -1123,7 +1123,7 @@
         <v>57</v>
       </c>
       <c r="N7" s="17" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -1133,8 +1133,8 @@
       <c r="B8" s="14">
         <v>630</v>
       </c>
-      <c r="C8" s="14">
-        <v>0</v>
+      <c r="C8" s="14" t="s">
+        <v>64</v>
       </c>
       <c r="D8" s="14">
         <v>180</v>
@@ -1169,18 +1169,18 @@
         <v>57</v>
       </c>
       <c r="N8" s="17" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="8">
         <v>46254</v>
       </c>
       <c r="B9" s="14">
         <v>360</v>
       </c>
-      <c r="C9" s="14">
-        <v>0</v>
+      <c r="C9" s="14" t="s">
+        <v>64</v>
       </c>
       <c r="D9" s="14">
         <v>300</v>
@@ -1206,16 +1206,16 @@
         <v>390</v>
       </c>
       <c r="K9" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M9" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="L9" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="M9" s="16" t="s">
-        <v>61</v>
-      </c>
       <c r="N9" s="17" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1225,8 +1225,8 @@
       <c r="B10" s="14">
         <v>510</v>
       </c>
-      <c r="C10" s="14">
-        <v>0</v>
+      <c r="C10" s="14" t="s">
+        <v>64</v>
       </c>
       <c r="D10" s="14">
         <v>360</v>
@@ -1261,18 +1261,18 @@
         <v>57</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="8">
         <v>46256</v>
       </c>
       <c r="B11" s="14">
         <v>240</v>
       </c>
-      <c r="C11" s="14">
-        <v>0</v>
+      <c r="C11" s="14" t="s">
+        <v>64</v>
       </c>
       <c r="D11" s="14">
         <v>390</v>
@@ -1298,16 +1298,16 @@
         <v>390</v>
       </c>
       <c r="K11" s="16" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="L11" s="16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="M11" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -1317,8 +1317,8 @@
       <c r="B12" s="14">
         <v>300</v>
       </c>
-      <c r="C12" s="14">
-        <v>0</v>
+      <c r="C12" s="14" t="s">
+        <v>64</v>
       </c>
       <c r="D12" s="14">
         <v>360</v>
@@ -1344,13 +1344,13 @@
         <v>340</v>
       </c>
       <c r="K12" s="16" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="L12" s="16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="M12" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N12" s="17"/>
     </row>
@@ -1361,8 +1361,8 @@
       <c r="B13" s="14">
         <v>270</v>
       </c>
-      <c r="C13" s="14">
-        <v>0</v>
+      <c r="C13" s="14" t="s">
+        <v>64</v>
       </c>
       <c r="D13" s="14">
         <v>240</v>
@@ -1398,15 +1398,15 @@
       </c>
       <c r="N13" s="17"/>
     </row>
-    <row r="14" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="8">
         <v>46259</v>
       </c>
       <c r="B14" s="14">
         <v>60</v>
       </c>
-      <c r="C14" s="14">
-        <v>0</v>
+      <c r="C14" s="14" t="s">
+        <v>64</v>
       </c>
       <c r="D14" s="14">
         <v>180</v>
@@ -1432,7 +1432,7 @@
         <v>700</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="L14" s="16" t="s">
         <v>56</v>
@@ -1441,7 +1441,7 @@
         <v>57</v>
       </c>
       <c r="N14" s="17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1451,8 +1451,8 @@
       <c r="B15" s="14">
         <v>420</v>
       </c>
-      <c r="C15" s="14">
-        <v>0</v>
+      <c r="C15" s="14" t="s">
+        <v>64</v>
       </c>
       <c r="D15" s="14">
         <v>210</v>
@@ -1487,7 +1487,7 @@
         <v>57</v>
       </c>
       <c r="N15" s="17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
@@ -1497,8 +1497,8 @@
       <c r="B16" s="14">
         <v>540</v>
       </c>
-      <c r="C16" s="14">
-        <v>0</v>
+      <c r="C16" s="14" t="s">
+        <v>64</v>
       </c>
       <c r="D16" s="14">
         <v>300</v>
@@ -1532,30 +1532,50 @@
       <c r="M16" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="N16" s="17" t="s">
-        <v>71</v>
-      </c>
+      <c r="N16" s="17"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="A17" s="8">
+        <v>46262</v>
+      </c>
+      <c r="B17" s="14">
+        <v>360</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="D17" s="14">
+        <v>330</v>
+      </c>
+      <c r="E17" s="14">
+        <v>180</v>
+      </c>
+      <c r="F17" s="14">
+        <v>3</v>
+      </c>
+      <c r="G17" s="14">
+        <v>150</v>
+      </c>
+      <c r="H17" s="14">
+        <v>150</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>1023</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
+        <v>417</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>60</v>
+      </c>
       <c r="N17" s="17"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">

--- a/12612645.xlsx
+++ b/12612645.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shash\Desktop\Activities\12612645\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BE94736-FA45-4150-93D4-29E4EE948DD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90D56AF0-3EE2-4180-851D-F8B1CE1C3EBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1579,69 +1579,135 @@
       <c r="N17" s="17"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="A18" s="8">
+        <v>46263</v>
+      </c>
+      <c r="B18" s="14">
+        <v>240</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="D18" s="14">
+        <v>360</v>
+      </c>
+      <c r="E18" s="14">
+        <v>210</v>
+      </c>
+      <c r="F18" s="14">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14">
+        <v>0</v>
+      </c>
+      <c r="H18" s="14">
+        <v>240</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
+        <v>390</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>60</v>
+      </c>
       <c r="N18" s="17"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="8">
+        <v>46264</v>
+      </c>
+      <c r="B19" s="14">
+        <v>360</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="D19" s="14">
+        <v>300</v>
+      </c>
+      <c r="E19" s="14">
+        <v>180</v>
+      </c>
+      <c r="F19" s="14">
+        <v>0</v>
+      </c>
+      <c r="G19" s="14">
+        <v>0</v>
+      </c>
+      <c r="H19" s="14">
+        <v>180</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
+        <v>420</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>60</v>
+      </c>
       <c r="N19" s="17"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="A20" s="8">
+        <v>46265</v>
+      </c>
+      <c r="B20" s="14">
+        <v>300</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20" s="14">
+        <v>300</v>
+      </c>
+      <c r="E20" s="14">
+        <v>120</v>
+      </c>
+      <c r="F20" s="14">
+        <v>3</v>
+      </c>
+      <c r="G20" s="14">
+        <v>150</v>
+      </c>
+      <c r="H20" s="14">
+        <v>120</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>843</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
+        <v>597</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>50</v>
+      </c>
       <c r="N20" s="17"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">

--- a/12612645.xlsx
+++ b/12612645.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shash\Desktop\Activities\12612645\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90D56AF0-3EE2-4180-851D-F8B1CE1C3EBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4366033A-A1C4-47FA-811F-9836E79033D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1680,7 +1680,7 @@
         <v>300</v>
       </c>
       <c r="E20" s="14">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="F20" s="14">
         <v>3</v>
@@ -1693,11 +1693,11 @@
       </c>
       <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v>843</v>
+        <v>873</v>
       </c>
       <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v>597</v>
+        <v>567</v>
       </c>
       <c r="K20" s="16" t="s">
         <v>62</v>

--- a/12612645.xlsx
+++ b/12612645.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shash\Desktop\Activities\12612645\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4366033A-A1C4-47FA-811F-9836E79033D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EA26450-DC32-4027-BB05-5BA04C36F89B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1711,25 +1711,47 @@
       <c r="N20" s="17"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="A21" s="8">
+        <v>46266</v>
+      </c>
+      <c r="B21" s="14">
+        <v>360</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="D21" s="14">
+        <v>240</v>
+      </c>
+      <c r="E21" s="14">
+        <v>210</v>
+      </c>
+      <c r="F21" s="14">
+        <v>4</v>
+      </c>
+      <c r="G21" s="14">
+        <v>200</v>
+      </c>
+      <c r="H21" s="14">
+        <v>180</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>994</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
+        <v>446</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>50</v>
+      </c>
       <c r="N21" s="17"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">

--- a/12612645.xlsx
+++ b/12612645.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shash\Desktop\Activities\12612645\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EA26450-DC32-4027-BB05-5BA04C36F89B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D700208-94CA-4533-AD31-05F754F95892}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1551,21 +1551,21 @@
         <v>180</v>
       </c>
       <c r="F17" s="14">
+        <v>150</v>
+      </c>
+      <c r="G17" s="14">
         <v>3</v>
-      </c>
-      <c r="G17" s="14">
-        <v>150</v>
       </c>
       <c r="H17" s="14">
         <v>150</v>
       </c>
       <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v>1023</v>
+        <v>1170</v>
       </c>
       <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v>417</v>
+        <v>270</v>
       </c>
       <c r="K17" s="16" t="s">
         <v>62</v>
@@ -1683,21 +1683,21 @@
         <v>150</v>
       </c>
       <c r="F20" s="14">
+        <v>150</v>
+      </c>
+      <c r="G20" s="14">
         <v>3</v>
-      </c>
-      <c r="G20" s="14">
-        <v>150</v>
       </c>
       <c r="H20" s="14">
         <v>120</v>
       </c>
       <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v>873</v>
+        <v>1020</v>
       </c>
       <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v>567</v>
+        <v>420</v>
       </c>
       <c r="K20" s="16" t="s">
         <v>62</v>
@@ -1727,21 +1727,21 @@
         <v>210</v>
       </c>
       <c r="F21" s="14">
+        <v>200</v>
+      </c>
+      <c r="G21" s="14">
         <v>4</v>
-      </c>
-      <c r="G21" s="14">
-        <v>200</v>
       </c>
       <c r="H21" s="14">
         <v>180</v>
       </c>
       <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v>994</v>
+        <v>1190</v>
       </c>
       <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v>446</v>
+        <v>250</v>
       </c>
       <c r="K21" s="16" t="s">
         <v>62</v>
@@ -1755,47 +1755,91 @@
       <c r="N21" s="17"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="A22" s="8">
+        <v>46267</v>
+      </c>
+      <c r="B22" s="14">
+        <v>240</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="D22" s="14">
+        <v>360</v>
+      </c>
+      <c r="E22" s="14">
+        <v>180</v>
+      </c>
+      <c r="F22" s="14">
+        <v>150</v>
+      </c>
+      <c r="G22" s="14">
+        <v>3</v>
+      </c>
+      <c r="H22" s="14">
+        <v>150</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
+        <v>360</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>60</v>
+      </c>
       <c r="N22" s="17"/>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+    <row r="23" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="8">
+        <v>46268</v>
+      </c>
+      <c r="B23" s="14">
+        <v>240</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="D23" s="14">
+        <v>300</v>
+      </c>
+      <c r="E23" s="14">
+        <v>240</v>
+      </c>
+      <c r="F23" s="14">
+        <v>200</v>
+      </c>
+      <c r="G23" s="14">
+        <v>4</v>
+      </c>
+      <c r="H23" s="14">
+        <v>240</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
+        <v>220</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>60</v>
+      </c>
       <c r="N23" s="17"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">

--- a/12612645.xlsx
+++ b/12612645.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shash\Desktop\Activities\12612645\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D700208-94CA-4533-AD31-05F754F95892}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C79F160-D525-4310-AE52-5265C9CD9945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1843,25 +1843,47 @@
       <c r="N23" s="17"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="A24" s="8">
+        <v>46269</v>
+      </c>
+      <c r="B24" s="14">
+        <v>90</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" s="14">
+        <v>180</v>
+      </c>
+      <c r="E24" s="14">
+        <v>240</v>
+      </c>
+      <c r="F24" s="14">
+        <v>4</v>
+      </c>
+      <c r="G24" s="14">
+        <v>200</v>
+      </c>
+      <c r="H24" s="14">
+        <v>300</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>814</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
+        <v>626</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N24" s="17"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">

--- a/12612645.xlsx
+++ b/12612645.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shash\Desktop\Activities\12612645\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C79F160-D525-4310-AE52-5265C9CD9945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4EF9565-E71C-49C1-B4C5-DAB719C7C7F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
     <sheet name="Daily Log" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1886,26 +1886,48 @@
       </c>
       <c r="N24" s="17"/>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+    <row r="25" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="8">
+        <v>46270</v>
+      </c>
+      <c r="B25" s="14">
+        <v>480</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="D25" s="14">
+        <v>300</v>
+      </c>
+      <c r="E25" s="14">
+        <v>120</v>
+      </c>
+      <c r="F25" s="14">
+        <v>0</v>
+      </c>
+      <c r="G25" s="14">
+        <v>0</v>
+      </c>
+      <c r="H25" s="14">
+        <v>180</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
+        <v>360</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>60</v>
+      </c>
       <c r="N25" s="17"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
